--- a/Result/checksun_type/移動控制.xlsx
+++ b/Result/checksun_type/移動控制.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>77.02000000000001</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>81.9</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>90.29</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>90.29000000000001</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>25541632.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>18478448.4</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>18478448.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>22340328.6</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>35628392.24</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>35628392.24</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-1689715.322497111</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>25541632</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>25541632.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>76.44000000000001</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>82.46</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>90.77</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>82.45999999999999</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>90.77</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>11993989.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>18530460.2</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>18530460.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>21012225.4</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>36928818.4</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>36928818.4</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-2447746.38427645</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>11993989</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>11993989.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>76.28</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>83.21</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>91.4</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>83.20999999999999</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>91.40000000000001</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>12838922.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>22521596.2</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>22521596.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>22945115.2</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>38908292.88</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>38908292.88</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-1991695.208808493</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>12838922</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>12838922.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>76.82000000000001</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>83.94</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>92.05</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>83.94</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>92.05</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>17519372.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>23921080.0</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>23921080</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>24389345.8</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>43309022.62</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>43309022.62</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-1359590.093539681</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>17519372</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>17519372.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>77.75999999999999</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>84.76</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>92.65</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>84.76000000000001</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>92.65000000000001</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>24498327.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>24703031.4</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>24703031.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>24565406.9</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>44269123.4</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>44269123.4</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-909502.7826721072</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>24498327</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>24498327.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>78.4</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>85.44</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>93.16</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>85.44</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>93.16</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>25801691.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>26202208.8</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>26202208.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>23518410.6</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>44891065.02</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>44891065.02</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-981783.8463372774</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>25801691</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>25801691.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>80.1</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>86.25</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>93.7</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>86.25</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>93.7</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>31949669.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>23493990.6</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>23493990.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>23233683.5</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>46183811.22</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>46183811.22</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-1189624.942775473</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>31949669</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>31949669.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>81.76</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>86.96</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>94.29</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>86.95999999999999</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>94.29000000000001</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>19836341.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>23368634.2</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>23368634.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>23837111.6</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>47827868.46</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>47827868.46</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-2102766.118302345</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>19836341</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>19836341.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>82.88</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>87.49</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>94.84</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>87.48999999999999</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>94.84</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>21429129.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>24857611.6</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>24857611.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>23731992.4</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>49953212.14</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>49953212.14</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-2034298.150544219</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>21429129</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>21429129.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>83.82000000000001</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>88.1</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>95.44</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>88.09999999999999</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>95.44</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>31994214.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>24427782.4</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>24427782.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>23576187.8</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>52965825.02</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>52965825.02</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-2034489.119798888</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>31994214</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>31994214.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>84.86</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>88.55</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>96.09</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>88.55</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>96.09</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>12260600.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>20834612.4</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>20834612.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>23290139.2</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>56233928.78</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>56233928.78</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-3094075.000169881</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>12260600</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>12260600.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>95.3</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>99.48</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>102.39</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>99.48</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>102.39</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>190.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>228.6</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>228.6</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>615.8</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>0</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-116.0675495277791</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>190</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>190.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>95.0</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>99.9</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>102.51</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>102.51</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>285.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>248.2</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>248.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>656.8</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>0</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-109.8053880083213</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>285</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>285.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>94.92</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>100.35</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>102.62</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>100.35</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>102.62</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>189.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>418.4</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>418.4</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>698.9</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>0</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-107.1163934087987</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>189</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>189.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>95.46000000000001</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>101.0</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>102.75</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>101</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>102.75</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>3.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>624.8</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>624.8</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>701.5</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>0</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-89.16367278773794</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>3</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>96.26</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>101.7</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>102.88</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>102.88</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>476.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>722.2</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>722.2</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>717.7</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>0</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-40.40394072951767</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>476</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>476.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>97.06</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>102.38</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>103.02</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>102.38</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>103.02</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>288.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>1003.0</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>1003</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>711.7</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>0</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-19.98275419172012</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>288</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>288.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>98.0</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>102.95</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>103.17</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>102.95</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>103.17</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>1136.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>1065.4</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>1065.4</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>776.1</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>0</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>30.04689636912349</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>1136</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>1136.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>98.88</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>103.4</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>103.26</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>103.26</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>1221.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>979.4</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>979.4</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>0</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>9.587579442859806</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>1221</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>1221.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>99.74</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>103.88</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>103.36</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>103.88</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>103.36</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>490.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>778.2</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>778.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>0</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-29.08957257476186</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>490</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>490.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>100.64</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>104.26</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>103.3</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>104.26</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>103.3</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>1880.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>713.2</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>713.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>0</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-4.982305007979676</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>1880</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>1880.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>101.44</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>104.68</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>103.23</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>104.68</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>103.23</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>600.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>420.4</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>420.4</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>0</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-119.2939833051487</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>600</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>600.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>43.26000000000001</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>45.32</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>48.57</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>45.32</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>48.57</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>923.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>639.2</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>639.2</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>649.6</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>966.14</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>966.14</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-131.9181011073526</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>923</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>923.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>43.41</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>45.57</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>48.75</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>45.57</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>48.75</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>519.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>498.8</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>498.8</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>1102.2</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>1091.02</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>1091.02</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-165.5805573496141</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>519</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>519.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>43.54</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>45.86</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>48.95</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>45.86</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>48.95</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>44.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>645.6</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>645.6</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>1107.5</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>1099.2</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>1099.2</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-164.4704749332157</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>44</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>44.15</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>46.21</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>49.14</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>46.21</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>49.14</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>957.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>797.0</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>797</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>1146.9</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>1109.02</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>1109.02</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-106.1178402336029</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>957</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>957.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>45.15</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>46.53</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>49.32</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>46.53</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>49.32</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>753.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>692.4</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>692.4</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>1094.2</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>1124.12</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>1124.12</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-116.7884392258132</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>753</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>753.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>45.91</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>46.82</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>49.48</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>46.82</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>49.48</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>221.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>660.0</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>660</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>1132.9</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>1171.46</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>1171.46</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-106.003993528049</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>221</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>221.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>46.72</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>47.15</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>49.68</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>47.15</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>49.68</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>1253.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>1705.6</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>1705.6</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>1264.1</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>1197.88</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>1197.88</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-29.8117856195272</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>1253</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>1253.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>47.47000000000001</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>47.51</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>49.89</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>47.51</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>49.89</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>801.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>1569.4</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>1569.4</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>1197.9</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>1178.44</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>1178.44</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-30.47249626379858</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>801</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>801.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>47.98999999999999</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>47.7</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>50.03</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>50.03</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>434.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>1496.8</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>1496.8</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>1365.5</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>1182.34</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>1182.34</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>18.10050625380677</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>434</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>434.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>47.45</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>47.81</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>50.12</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>47.81</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>50.12</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>591.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>1496.0</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>1496</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>1788.7</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>1213.76</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>1213.76</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>126.1654917698927</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>591</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>591.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>47.42</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>47.92</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>50.23</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>47.92</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>50.23</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>5449.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>1605.8</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>1605.8</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>1990.9</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>1227.62</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>1227.62</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>259.2167035153764</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>5449</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>5449.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>118.5</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>123.48</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>129.32</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>123.48</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>129.32</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>6660.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>12370.4</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>12370.4</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>11313.9</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>10664.12</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>10664.12</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>290.3377297371826</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>6660</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>6660.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>118.0</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>124.02</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>129.76</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>124.02</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>129.76</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>29419.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>11922.2</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>11922.2</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>11723.9</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>10870.2</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>10870.2</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>944.5084424789566</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>29419</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>29419.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>116.9</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>124.38</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>130.18</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>124.38</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>130.18</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>5943.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>9621.2</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>9621.200000000001</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>9433.9</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>10840.14</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>10840.14</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-593.1586979784715</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>5943</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>5943.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>117.0</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>124.92</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>130.66</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>124.92</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>130.66</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>10780.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>12262.6</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>12262.6</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>10051.1</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>10994.02</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>10994.02</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>-253.3560879898541</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>10780</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>10780.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>118.4</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>125.62</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>131.24</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>125.62</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>131.24</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>9050.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>11437.4</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>11437.4</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>12216.8</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>11031.66</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>11031.66</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>-277.1253562921902</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>9050</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>9050.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>119.7</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>126.25</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>131.73</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>126.25</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>131.73</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>4419.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>10257.4</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>10257.4</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>11815.6</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>11063.98</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>11063.98</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>-115.8269768565206</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>4419</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>4419.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>121.4</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>126.92</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>132.23</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>126.92</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>132.23</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>17914.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>11525.6</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>11525.6</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>13900.8</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>11172.64</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>11172.64</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>614.9145286535986</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>17914</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>17914.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>123.6</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>127.58</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>132.75</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>127.58</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>132.75</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>19150.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>9246.6</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>9246.6</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>13869.8</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>11003.34</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>11003.34</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>190.9768747875678</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>19150</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>19150.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>125.2</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>128.1</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>133.25</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>128.1</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>133.25</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>6654.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>7839.6</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>7839.6</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>13568.0</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>10936.96</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>10936.96</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>-553.8975191206046</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>6654</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>6654.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>125.4</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>128.48</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>133.68</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>128.48</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>133.68</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>3150.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>12996.2</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>12996.2</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>13330.6</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>11162.8</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>11162.8</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>-259.3645990208279</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>3150</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>3150.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>125.8</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>128.78</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>134.13</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>128.78</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>134.13</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>10760.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>13373.8</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>13373.8</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>13784.3</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>11403.4</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>11403.4</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>546.0883082295968</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>10760</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>10760.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20055,11 +19791,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
           <t>5209</t>
@@ -20241,41 +19973,37 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
+      <c r="AM46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO46" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AN46" t="inlineStr">
+      <c r="AP46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AS46" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AP46" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ46" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR46" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AS46" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AT46" t="inlineStr">
         <is>
           <t>0</t>
@@ -20296,20 +20024,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>0</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>0</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20050,10 @@
           <t>0</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>0</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20219,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20403,11 @@
           <t>203.0</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>217.92</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>229.57</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>217.92</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>229.57</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20454,16 @@
           <t>246990.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>261303.6</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>261303.6</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>360072.2</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>1087687.9</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>1087687.9</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20480,10 @@
           <t>-60756.27700912725</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>246990</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>246990.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20649,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20833,11 @@
           <t>201.2</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>219.42</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>229.64</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>219.42</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>229.64</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20884,16 @@
           <t>188584.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>277235.2</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>277235.2</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>364259.9</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>1109012.44</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>1109012.44</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20910,10 @@
           <t>-62901.108610934</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>188584</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>188584.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21079,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21263,11 @@
           <t>200.9</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>221.0</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>229.9</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>221</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>229.9</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21314,16 @@
           <t>266834.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>327128.4</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>327128.4</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>378625.9</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>1132112.48</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>1132112.48</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21340,10 @@
           <t>-57460.89987741027</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>266834</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>266834.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21509,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21693,11 @@
           <t>203.5</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>223.02</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>230.31</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>223.02</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>230.31</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21744,16 @@
           <t>328496.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>351582.6</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>351582.6</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>393659.8</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>1170503.62</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>1170503.62</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21770,10 @@
           <t>-56020.92669104022</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>328496</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>328496.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21939,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22123,11 @@
           <t>206.5</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>225.2</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>230.45</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>225.2</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>230.45</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22174,16 @@
           <t>275614.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>419383.0</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>419383</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>399217.9</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>1181679.14</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>1181679.14</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22200,10 @@
           <t>-58569.71761440305</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>275614</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>275614.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22369,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22553,11 @@
           <t>209.8</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>227.1</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>230.35</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>227.1</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>230.35</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22604,16 @@
           <t>326648.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>458840.8</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>458840.8</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>399885.8</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>1187183.2</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>1187183.2</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22630,10 @@
           <t>-54453.1433044069</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>326648</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>326648.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22799,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22983,11 @@
           <t>214.9</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>229.28</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>230.34</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>229.28</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>230.34</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23034,16 @@
           <t>438050.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>451284.6</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>451284.6</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>403006.7</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>1190565.96</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>1190565.96</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23060,10 @@
           <t>-52095.49631496938</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>438050</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>438050.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23229,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23413,11 @@
           <t>219.1</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>230.98</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>230.29</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>230.98</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>230.29</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23464,16 @@
           <t>389105.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>430123.4</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>430123.4</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>398138.1</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>1191948.4</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>1191948.4</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23490,10 @@
           <t>-58802.80431880965</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>389105</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>389105.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23659,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23843,11 @@
           <t>222.5</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>232.15</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>229.96</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>232.15</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>229.96</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23894,16 @@
           <t>667498.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>435737.0</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>435737</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>393344.8</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>1189336.42</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>1189336.42</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23920,10 @@
           <t>-61040.46559862403</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>667498</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>667498.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24089,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24273,11 @@
           <t>225.1</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>233.28</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>229.57</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>233.28</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>229.57</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24324,16 @@
           <t>472903.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>379052.8</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>379052.8</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>373683.5</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>1181965.28</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>1181965.28</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24350,10 @@
           <t>-91884.92936983652</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>472903</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>472903.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24519,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24703,11 @@
           <t>226.8</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>233.52</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>229.07</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>233.52</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>229.07</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24754,16 @@
           <t>288867.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>340930.8</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>340930.8</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>402140.3</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>1178670.4</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>1178670.4</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24780,10 @@
           <t>-111817.3801369317</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>288867</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>288867.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24949,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25133,11 @@
           <t>586.6</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>636.0</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>667.3</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>636</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>667.3</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25184,16 @@
           <t>2251806679.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>2845492684.8</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>2845492684.8</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>3254023064.0</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>2250939639.92</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>2250939639.92</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25210,10 @@
           <t>80988449.20909452</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>2251806679</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>2251806679.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25379,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25563,11 @@
           <t>577.4</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>640.85</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>668.88</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>640.85</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>668.88</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25614,16 @@
           <t>2303990317.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>2895931468.2</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>2895931468.2</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>3423927956.4</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>2313304958.2</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>2313304958.2</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25640,10 @@
           <t>168000892.6023631</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>2303990317</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>2303990317.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25809,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25993,11 @@
           <t>572.0</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>646.8</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>670.44</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>646.8</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>670.4400000000001</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26044,16 @@
           <t>4282414081.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>3701315712.0</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>3701315712</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>3406103963.5</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>2315429027.54</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>2315429027.54</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26070,10 @@
           <t>280713247.2140913</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>4282414081</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>4282414081.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26239,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26423,11 @@
           <t>577.0</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>653.25</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>671.96</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>653.25</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>671.96</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26474,16 @@
           <t>3277325446.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>3639148367.2</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>3639148367.2</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>3149911827.2</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>2279747515.3</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>2279747515.3</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26500,10 @@
           <t>219731448.8303423</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>3277325446</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>3277325446.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26669,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26853,11 @@
           <t>589.0</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>659.5</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>673.4</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>659.5</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>673.4</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26904,16 @@
           <t>2111926901.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>3434438489.8</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>3434438489.8</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>3061336173.2</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>2234436035.54</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>2234436035.54</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26930,10 @@
           <t>232455110.2881894</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>2111926901</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>2111926901.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27099,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27283,11 @@
           <t>601.0</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>665.8</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>674.84</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>665.8</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>674.84</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27334,16 @@
           <t>2504000596.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>3662553443.2</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>3662553443.2</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>3053660242.7</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>2215412102.28</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>2215412102.28</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27360,10 @@
           <t>367193931.1105347</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>2504000596</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>2504000596.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27529,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27713,11 @@
           <t>617.2</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>672.05</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>676.22</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>672.05</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>676.22</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27764,16 @@
           <t>6330911536.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>3951924444.6</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>3951924444.6</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>3034497195.4</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>2193079344.64</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>2193079344.64</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27790,10 @@
           <t>504555995.9956522</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>6330911536</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>6330911536.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27959,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28143,11 @@
           <t>636.8</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>678.2</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>677.46</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>678.2</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>677.46</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28194,16 @@
           <t>3971577357.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>3110892215.0</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>3110892215</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>2577610128.3</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>2089597881.18</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>2089597881.18</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28220,10 @@
           <t>272741488.1174035</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>3971577357</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>3971577357.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28389,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28573,11 @@
           <t>647.4</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>681.95</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>677.64</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>681.95</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>677.64</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28624,16 @@
           <t>2253776059.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>2660675287.2</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>2660675287.2</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>2395309044.8</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>2031062259.28</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>2031062259.28</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28650,10 @@
           <t>184622942.8942842</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>2253776059</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>2253776059.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28819,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29003,11 @@
           <t>653.6</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>684.55</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>677.36</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>684.55</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>677.36</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29054,16 @@
           <t>3252501668.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>2688233856.6</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>2688233856.6</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>2353124375.3</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>2012331643.46</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>2012331643.46</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29080,10 @@
           <t>236195769.4007463</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>3252501668</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>3252501668.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
@@ -29649,7 +29249,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -29833,15 +29433,11 @@
           <t>663.2</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>687.1</t>
-        </is>
-      </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>677.34</t>
-        </is>
+      <c r="AM68" t="n">
+        <v>687.1</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>677.34</v>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
@@ -29888,20 +29484,16 @@
           <t>3950855603.0</t>
         </is>
       </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>2444767042.2</t>
-        </is>
+      <c r="AX68" t="n">
+        <v>2444767042.2</v>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
           <t>2195634921.6</t>
         </is>
       </c>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>1973519631.2</t>
-        </is>
+      <c r="AZ68" t="n">
+        <v>1973519631.2</v>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
@@ -29918,8 +29510,10 @@
           <t>194429357.3956661</t>
         </is>
       </c>
-      <c r="BD68" t="n">
-        <v>3950855603</v>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>3950855603.0</t>
+        </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
@@ -30085,7 +29679,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -30269,15 +29863,11 @@
           <t>91.34</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>103.07</t>
-        </is>
-      </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>103.31</t>
-        </is>
+      <c r="AM69" t="n">
+        <v>103.07</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>103.31</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
@@ -30324,20 +29914,16 @@
           <t>2683545818.0</t>
         </is>
       </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>5000685349.4</t>
-        </is>
+      <c r="AX69" t="n">
+        <v>5000685349.4</v>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
           <t>4727097624.7</t>
         </is>
       </c>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>6863428946.3</t>
-        </is>
+      <c r="AZ69" t="n">
+        <v>6863428946.3</v>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
@@ -30354,8 +29940,10 @@
           <t>-78239912.41163445</t>
         </is>
       </c>
-      <c r="BD69" t="n">
-        <v>2683545818</v>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>2683545818.0</t>
+        </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
@@ -30521,7 +30109,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -30705,15 +30293,11 @@
           <t>92.5</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>104.44</t>
-        </is>
-      </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>103.43</t>
-        </is>
+      <c r="AM70" t="n">
+        <v>104.44</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>103.43</v>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
@@ -30760,20 +30344,16 @@
           <t>4682266073.0</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>5019578044.4</t>
-        </is>
+      <c r="AX70" t="n">
+        <v>5019578044.4</v>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
           <t>4597307742.4</t>
         </is>
       </c>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>7180754379.14</t>
-        </is>
+      <c r="AZ70" t="n">
+        <v>7180754379.14</v>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
@@ -30790,8 +30370,10 @@
           <t>116188863.3358154</t>
         </is>
       </c>
-      <c r="BD70" t="n">
-        <v>4682266073</v>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>4682266073.0</t>
+        </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
@@ -30957,7 +30539,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -31141,15 +30723,11 @@
           <t>93.56</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>105.81</t>
-        </is>
-      </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>103.41</t>
-        </is>
+      <c r="AM71" t="n">
+        <v>105.81</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>103.41</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
@@ -31196,20 +30774,16 @@
           <t>11515775721.0</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>4696916791.4</t>
-        </is>
+      <c r="AX71" t="n">
+        <v>4696916791.4</v>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
           <t>4341077616.0</t>
         </is>
       </c>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>7241408797.74</t>
-        </is>
+      <c r="AZ71" t="n">
+        <v>7241408797.74</v>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
@@ -31226,8 +30800,10 @@
           <t>175646056.2487507</t>
         </is>
       </c>
-      <c r="BD71" t="n">
-        <v>11515775721</v>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>11515775721.0</t>
+        </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
@@ -31393,7 +30969,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31577,15 +31153,11 @@
           <t>94.3</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>106.92</t>
-        </is>
-      </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>103.14</t>
-        </is>
+      <c r="AM72" t="n">
+        <v>106.92</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>103.14</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
@@ -31632,20 +31204,16 @@
           <t>3032171594.0</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>3191641823.4</t>
-        </is>
+      <c r="AX72" t="n">
+        <v>3191641823.4</v>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
           <t>3527299622.7</t>
         </is>
       </c>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>7285669264.58</t>
-        </is>
+      <c r="AZ72" t="n">
+        <v>7285669264.58</v>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
@@ -31662,8 +31230,10 @@
           <t>-477849918.1702256</t>
         </is>
       </c>
-      <c r="BD72" t="n">
-        <v>3032171594</v>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>3032171594.0</t>
+        </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
@@ -31829,7 +31399,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -32013,15 +31583,11 @@
           <t>95.85999999999999</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>108.02</t>
-        </is>
-      </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>102.75</t>
-        </is>
+      <c r="AM73" t="n">
+        <v>108.02</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>102.75</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
@@ -32068,20 +31634,16 @@
           <t>3089667541.0</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>4058514408.6</t>
-        </is>
+      <c r="AX73" t="n">
+        <v>4058514408.6</v>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
           <t>3531039856.9</t>
         </is>
       </c>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>7317342463.3</t>
-        </is>
+      <c r="AZ73" t="n">
+        <v>7317342463.3</v>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
@@ -32098,8 +31660,10 @@
           <t>-485391942.3698263</t>
         </is>
       </c>
-      <c r="BD73" t="n">
-        <v>3089667541</v>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>3089667541.0</t>
+        </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
@@ -32265,7 +31829,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -32449,15 +32013,11 @@
           <t>98.74</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>109.04</t>
-        </is>
-      </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>102.19</t>
-        </is>
+      <c r="AM74" t="n">
+        <v>109.04</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>102.19</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
@@ -32504,20 +32064,16 @@
           <t>2778009293.0</t>
         </is>
       </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>4453509900.0</t>
-        </is>
+      <c r="AX74" t="n">
+        <v>4453509900</v>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
           <t>3688316666.2</t>
         </is>
       </c>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>7280178623.2</t>
-        </is>
+      <c r="AZ74" t="n">
+        <v>7280178623.2</v>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
@@ -32534,8 +32090,10 @@
           <t>-484991116.1774759</t>
         </is>
       </c>
-      <c r="BD74" t="n">
-        <v>2778009293</v>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>2778009293.0</t>
+        </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
@@ -32701,7 +32259,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -32885,15 +32443,11 @@
           <t>101.34</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>110.06</t>
-        </is>
-      </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>101.66</t>
-        </is>
+      <c r="AM75" t="n">
+        <v>110.06</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>101.66</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
@@ -32940,20 +32494,16 @@
           <t>3068959808.0</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>4175037440.4</t>
-        </is>
+      <c r="AX75" t="n">
+        <v>4175037440.4</v>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
           <t>3901577638.9</t>
         </is>
       </c>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>7265450343.64</t>
-        </is>
+      <c r="AZ75" t="n">
+        <v>7265450343.64</v>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
@@ -32970,8 +32520,10 @@
           <t>-433705440.8963513</t>
         </is>
       </c>
-      <c r="BD75" t="n">
-        <v>3068959808</v>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>3068959808.0</t>
+        </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
@@ -33137,7 +32689,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -33321,15 +32873,11 @@
           <t>103.48</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>111.34</t>
-        </is>
-      </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>101.12</t>
-        </is>
+      <c r="AM76" t="n">
+        <v>111.34</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>101.12</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
@@ -33376,20 +32924,16 @@
           <t>3989400881.0</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>3985238440.6</t>
-        </is>
+      <c r="AX76" t="n">
+        <v>3985238440.6</v>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
           <t>3979054603.6</t>
         </is>
       </c>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>7220968787.64</t>
-        </is>
+      <c r="AZ76" t="n">
+        <v>7220968787.64</v>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
@@ -33406,8 +32950,10 @@
           <t>-376123979.9270172</t>
         </is>
       </c>
-      <c r="BD76" t="n">
-        <v>3989400881</v>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>3989400881.0</t>
+        </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
@@ -33573,7 +33119,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -33757,15 +33303,11 @@
           <t>105.36</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>111.96</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>100.52</t>
-        </is>
+      <c r="AM77" t="n">
+        <v>111.96</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>100.52</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
@@ -33812,20 +33354,16 @@
           <t>7366534520.0</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>3862957422.0</t>
-        </is>
+      <c r="AX77" t="n">
+        <v>3862957422</v>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
           <t>4011436058.8</t>
         </is>
       </c>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>7171595467.56</t>
-        </is>
+      <c r="AZ77" t="n">
+        <v>7171595467.56</v>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
@@ -33842,8 +33380,10 @@
           <t>-379050437.0805759</t>
         </is>
       </c>
-      <c r="BD77" t="n">
-        <v>7366534520</v>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>7366534520.0</t>
+        </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
@@ -34009,7 +33549,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -34193,15 +33733,11 @@
           <t>107.2</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>112.52</t>
-        </is>
-      </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>99.87</t>
-        </is>
+      <c r="AM78" t="n">
+        <v>112.52</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>99.87</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
@@ -34248,20 +33784,16 @@
           <t>5064644998.0</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>3003565305.2</t>
-        </is>
+      <c r="AX78" t="n">
+        <v>3003565305.2</v>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
           <t>4108066698.5</t>
         </is>
       </c>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>7070679471.22</t>
-        </is>
+      <c r="AZ78" t="n">
+        <v>7070679471.22</v>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
@@ -34278,8 +33810,10 @@
           <t>-731529321.5827818</t>
         </is>
       </c>
-      <c r="BD78" t="n">
-        <v>5064644998</v>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>5064644998.0</t>
+        </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
@@ -34445,7 +33979,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -34629,15 +34163,11 @@
           <t>107.6</t>
         </is>
       </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>112.4</t>
-        </is>
-      </c>
-      <c r="AN79" t="inlineStr">
-        <is>
-          <t>99.02</t>
-        </is>
+      <c r="AM79" t="n">
+        <v>112.4</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>99.02</v>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
@@ -34684,20 +34214,16 @@
           <t>1385646995.0</t>
         </is>
       </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>2923123432.4</t>
-        </is>
+      <c r="AX79" t="n">
+        <v>2923123432.4</v>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
           <t>4157974302.6</t>
         </is>
       </c>
-      <c r="AZ79" t="inlineStr">
-        <is>
-          <t>7004676232.68</t>
-        </is>
+      <c r="AZ79" t="n">
+        <v>7004676232.68</v>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
@@ -34714,8 +34240,10 @@
           <t>-962313517.7436905</t>
         </is>
       </c>
-      <c r="BD79" t="n">
-        <v>1385646995</v>
+      <c r="BD79" t="inlineStr">
+        <is>
+          <t>1385646995.0</t>
+        </is>
       </c>
       <c r="BE79" t="inlineStr">
         <is>
